--- a/SubRES_TMPL/SubRES_SRV_NewTechs_Trans.xlsx
+++ b/SubRES_TMPL/SubRES_SRV_NewTechs_Trans.xlsx
@@ -565,12 +565,6 @@
     <t>BASE</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -1129,6 +1123,108 @@
     <t>~TFM_Fill-R: w=BY_S-SC; Hcol=Region</t>
   </si>
   <si>
+    <t>S-PLIG-PU_X2</t>
+  </si>
+  <si>
+    <t>SRVWH-PU</t>
+  </si>
+  <si>
+    <t>SRVWH-CS</t>
+  </si>
+  <si>
+    <t>SRVSC-PU</t>
+  </si>
+  <si>
+    <t>SRVSC-CS</t>
+  </si>
+  <si>
+    <t>~TFM_UPD</t>
+  </si>
+  <si>
+    <t>AFA for SRV techs</t>
+  </si>
+  <si>
+    <t>EFF for SRV techs</t>
+  </si>
+  <si>
+    <t>CEFF</t>
+  </si>
+  <si>
+    <t>~TFM_Fill-R: w=BY_S-EAP; Hcol=Region</t>
+  </si>
+  <si>
+    <t>S-LIG*, S-REF*, S-OEL*, S-PLIG*</t>
+  </si>
+  <si>
+    <t>*Electric appliances</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>S-PLIG*</t>
+  </si>
+  <si>
+    <t>EFF*Stock</t>
+  </si>
+  <si>
+    <t>TIMES-Ireland Model</t>
+  </si>
+  <si>
+    <t>Sector(s):</t>
+  </si>
+  <si>
+    <t>Purpose:</t>
+  </si>
+  <si>
+    <t>Original developer(s):</t>
+  </si>
+  <si>
+    <t>Current maintainer(s):</t>
+  </si>
+  <si>
+    <t>Part of TIM version:</t>
+  </si>
+  <si>
+    <t>Model repository:</t>
+  </si>
+  <si>
+    <t>https://github.com/MaREI-EPMG/TIMES-Ireland-model</t>
+  </si>
+  <si>
+    <t>Licence:</t>
+  </si>
+  <si>
+    <t>CC BY-NC-SA 4.0 (unless specified otherwise)</t>
+  </si>
+  <si>
+    <t>https://creativecommons.org/licenses/by-nc-sa/4.0/</t>
+  </si>
+  <si>
+    <t>New Technologies - Transformation</t>
+  </si>
+  <si>
+    <t>Service sector (SRV)</t>
+  </si>
+  <si>
+    <t>Transform techno-economic data</t>
+  </si>
+  <si>
+    <t>Olexandr Balyk (UCC, olexandr.balyk@ucc.ie)</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>UP</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>S-SH-PU_OIL_X0</t>
+  </si>
+  <si>
     <t>S-SH-PU_LPG_X0</t>
   </si>
   <si>
@@ -1171,187 +1267,91 @@
     <t>S-SH-CS_BIO_X0</t>
   </si>
   <si>
-    <t>2018</t>
+    <t>ANNUAL</t>
+  </si>
+  <si>
+    <t>S-WH-PU_SOL_X0</t>
+  </si>
+  <si>
+    <t>S-WH-PU_OIL_X0</t>
+  </si>
+  <si>
+    <t>S-WH-PU_LPG_X0</t>
+  </si>
+  <si>
+    <t>S-WH-PU_GAS_X0</t>
+  </si>
+  <si>
+    <t>S-WH-PU_ELC_X0</t>
+  </si>
+  <si>
+    <t>S-WH-PU_COA_X0</t>
+  </si>
+  <si>
+    <t>S-WH-PU_BIO_X0</t>
+  </si>
+  <si>
+    <t>S-WH-CS_SOL_X0</t>
+  </si>
+  <si>
+    <t>S-WH-CS_OIL_X0</t>
+  </si>
+  <si>
+    <t>S-WH-CS_LPG_X0</t>
+  </si>
+  <si>
+    <t>S-WH-CS_GAS_X0</t>
+  </si>
+  <si>
+    <t>S-WH-CS_ELC_X0</t>
+  </si>
+  <si>
+    <t>S-WH-CS_COA_X0</t>
+  </si>
+  <si>
+    <t>S-WH-CS_BIO_X0</t>
+  </si>
+  <si>
+    <t>S-SC-PU_GAS_X0</t>
+  </si>
+  <si>
+    <t>S-SC-PU_ELC_X0</t>
+  </si>
+  <si>
+    <t>S-SC-CS_GAS_X0</t>
+  </si>
+  <si>
+    <t>S-SC-CS_ELC_X0</t>
+  </si>
+  <si>
+    <t>S-PLIG-PU_X1</t>
+  </si>
+  <si>
+    <t>S-LIG-PU_ELC_X0</t>
+  </si>
+  <si>
+    <t>S-LIG-CS_ELC_X0</t>
+  </si>
+  <si>
+    <t>S-PLIG-PU_X4</t>
+  </si>
+  <si>
+    <t>S-PLIG-PU_X3</t>
+  </si>
+  <si>
+    <t>S-REF-PU_ELC_X0</t>
+  </si>
+  <si>
+    <t>S-REF-CS_ELC_X0</t>
+  </si>
+  <si>
+    <t>S-OEL-PU_ELC_X0</t>
+  </si>
+  <si>
+    <t>S-OEL-CS_ELC_X0</t>
   </si>
   <si>
     <t>year2</t>
-  </si>
-  <si>
-    <t>ANNUAL</t>
-  </si>
-  <si>
-    <t>S-WH-PU_SOL_X0</t>
-  </si>
-  <si>
-    <t>S-WH-PU_OIL_X0</t>
-  </si>
-  <si>
-    <t>S-WH-PU_LPG_X0</t>
-  </si>
-  <si>
-    <t>S-WH-PU_GAS_X0</t>
-  </si>
-  <si>
-    <t>S-WH-PU_ELC_X0</t>
-  </si>
-  <si>
-    <t>S-WH-PU_COA_X0</t>
-  </si>
-  <si>
-    <t>S-WH-PU_BIO_X0</t>
-  </si>
-  <si>
-    <t>S-WH-CS_SOL_X0</t>
-  </si>
-  <si>
-    <t>S-WH-CS_OIL_X0</t>
-  </si>
-  <si>
-    <t>S-WH-CS_LPG_X0</t>
-  </si>
-  <si>
-    <t>S-WH-CS_GAS_X0</t>
-  </si>
-  <si>
-    <t>S-WH-CS_ELC_X0</t>
-  </si>
-  <si>
-    <t>S-WH-CS_COA_X0</t>
-  </si>
-  <si>
-    <t>S-WH-CS_BIO_X0</t>
-  </si>
-  <si>
-    <t>S-SC-PU_GAS_X0</t>
-  </si>
-  <si>
-    <t>S-SC-PU_ELC_X0</t>
-  </si>
-  <si>
-    <t>S-SC-CS_GAS_X0</t>
-  </si>
-  <si>
-    <t>S-SC-CS_ELC_X0</t>
-  </si>
-  <si>
-    <t>SRVWH-PU</t>
-  </si>
-  <si>
-    <t>SRVWH-CS</t>
-  </si>
-  <si>
-    <t>SRVSC-PU</t>
-  </si>
-  <si>
-    <t>SRVSC-CS</t>
-  </si>
-  <si>
-    <t>~TFM_UPD</t>
-  </si>
-  <si>
-    <t>AFA for SRV techs</t>
-  </si>
-  <si>
-    <t>EFF for SRV techs</t>
-  </si>
-  <si>
-    <t>CEFF</t>
-  </si>
-  <si>
-    <t>~TFM_Fill-R: w=BY_S-EAP; Hcol=Region</t>
-  </si>
-  <si>
-    <t>S-LIG*, S-REF*, S-OEL*, S-PLIG*</t>
-  </si>
-  <si>
-    <t>S-LIG-PU_ELC_X0</t>
-  </si>
-  <si>
-    <t>S-LIG-CS_ELC_X0</t>
-  </si>
-  <si>
-    <t>S-OEL-PU_ELC_X0</t>
-  </si>
-  <si>
-    <t>S-OEL-CS_ELC_X0</t>
-  </si>
-  <si>
-    <t>S-PLIG-PU_X2</t>
-  </si>
-  <si>
-    <t>S-PLIG-PU_X1</t>
-  </si>
-  <si>
-    <t>S-PLIG-PU_X4</t>
-  </si>
-  <si>
-    <t>S-PLIG-PU_X3</t>
-  </si>
-  <si>
-    <t>S-REF-PU_ELC_X0</t>
-  </si>
-  <si>
-    <t>S-REF-CS_ELC_X0</t>
-  </si>
-  <si>
-    <t>*Electric appliances</t>
-  </si>
-  <si>
-    <t>Stock</t>
-  </si>
-  <si>
-    <t>S-PLIG*</t>
-  </si>
-  <si>
-    <t>EFF*Stock</t>
-  </si>
-  <si>
-    <t>TIMES-Ireland Model</t>
-  </si>
-  <si>
-    <t>Sector(s):</t>
-  </si>
-  <si>
-    <t>Purpose:</t>
-  </si>
-  <si>
-    <t>Original developer(s):</t>
-  </si>
-  <si>
-    <t>Current maintainer(s):</t>
-  </si>
-  <si>
-    <t>Part of TIM version:</t>
-  </si>
-  <si>
-    <t>Model repository:</t>
-  </si>
-  <si>
-    <t>https://github.com/MaREI-EPMG/TIMES-Ireland-model</t>
-  </si>
-  <si>
-    <t>Licence:</t>
-  </si>
-  <si>
-    <t>CC BY-NC-SA 4.0 (unless specified otherwise)</t>
-  </si>
-  <si>
-    <t>https://creativecommons.org/licenses/by-nc-sa/4.0/</t>
-  </si>
-  <si>
-    <t>New Technologies - Transformation</t>
-  </si>
-  <si>
-    <t>Service sector (SRV)</t>
-  </si>
-  <si>
-    <t>Transform techno-economic data</t>
-  </si>
-  <si>
-    <t>Olexandr Balyk (UCC, olexandr.balyk@ucc.ie)</t>
-  </si>
-  <si>
-    <t>S-SH-PU_OIL_X0</t>
   </si>
   <si>
     <t>S-SH-PU_SOL_X0</t>
@@ -1517,14 +1517,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="7" tint="-0.499430000782013"/>
+      <color theme="7" tint="-0.498849987983704"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="7" tint="-0.499430000782013"/>
+      <color theme="7" tint="-0.498849987983704"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1559,7 +1559,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.0494400002062321"/>
+        <fgColor theme="0" tint="-0.0488599985837936"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1613,7 +1613,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1494500041008"/>
+        <fgColor theme="0" tint="-0.148870006203651"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2261,7 +2261,7 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId2"/>
-        <a:srcRect l="4536" t="8851" r="7664" b="12843"/>
+        <a:srcRect l="4447" t="8763" r="7575" b="12754"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2388,7 +2388,7 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId5"/>
-        <a:srcRect l="1286" t="6481" r="3929" b="6254"/>
+        <a:srcRect l="1197" t="6393" r="3840" b="6250"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2431,7 +2431,7 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId6"/>
-        <a:srcRect l="3916" t="26116" r="3916" b="26115"/>
+        <a:srcRect l="3828" t="26028" r="3828" b="26026"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3378,7 +3378,7 @@
     </row>
     <row r="16" spans="1:26" ht="102.75" customHeight="1">
       <c r="A16" s="75" t="s">
-        <v>258</v>
+        <v>212</v>
       </c>
       <c r="B16" s="75"/>
       <c r="C16" s="75"/>
@@ -3464,10 +3464,10 @@
     </row>
     <row r="19" spans="1:26" ht="17.25" customHeight="1">
       <c r="A19" s="66" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B19" s="74" t="s">
-        <v>269</v>
+        <v>223</v>
       </c>
       <c r="C19" s="74"/>
       <c r="D19" s="74"/>
@@ -3496,10 +3496,10 @@
     </row>
     <row r="20" spans="1:26" ht="17.25" customHeight="1">
       <c r="A20" s="66" t="s">
-        <v>259</v>
+        <v>213</v>
       </c>
       <c r="B20" s="74" t="s">
-        <v>270</v>
+        <v>224</v>
       </c>
       <c r="C20" s="74"/>
       <c r="D20" s="74"/>
@@ -3528,10 +3528,10 @@
     </row>
     <row r="21" spans="1:26" ht="17.25" customHeight="1">
       <c r="A21" s="66" t="s">
-        <v>260</v>
+        <v>214</v>
       </c>
       <c r="B21" s="69" t="s">
-        <v>271</v>
+        <v>225</v>
       </c>
       <c r="C21" s="69"/>
       <c r="D21" s="69"/>
@@ -3588,7 +3588,7 @@
     </row>
     <row r="23" spans="1:26" ht="17.25" customHeight="1">
       <c r="A23" s="66" t="s">
-        <v>261</v>
+        <v>215</v>
       </c>
       <c r="B23" s="74"/>
       <c r="C23" s="74"/>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="26" spans="1:26" ht="17.25" customHeight="1">
       <c r="A26" s="66" t="s">
-        <v>262</v>
+        <v>216</v>
       </c>
       <c r="B26" s="74" t="s">
-        <v>272</v>
+        <v>226</v>
       </c>
       <c r="C26" s="74"/>
       <c r="D26" s="74"/>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="29" spans="1:26" ht="17.25" customHeight="1">
       <c r="A29" s="66" t="s">
-        <v>263</v>
+        <v>217</v>
       </c>
       <c r="B29" s="70">
         <v>1</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="30" spans="1:26" ht="17.25" customHeight="1">
       <c r="A30" s="66" t="s">
-        <v>264</v>
+        <v>218</v>
       </c>
       <c r="B30" s="76" t="s">
-        <v>265</v>
+        <v>219</v>
       </c>
       <c r="C30" s="74"/>
       <c r="D30" s="74"/>
@@ -3826,10 +3826,10 @@
     </row>
     <row r="31" spans="1:26" ht="17.25" customHeight="1">
       <c r="A31" s="66" t="s">
-        <v>266</v>
+        <v>220</v>
       </c>
       <c r="B31" s="74" t="s">
-        <v>267</v>
+        <v>221</v>
       </c>
       <c r="C31" s="74"/>
       <c r="D31" s="74"/>
@@ -3859,7 +3859,7 @@
     <row r="32" spans="1:26" ht="17.25" customHeight="1">
       <c r="A32" s="72"/>
       <c r="B32" s="73" t="s">
-        <v>268</v>
+        <v>222</v>
       </c>
       <c r="C32" s="72"/>
       <c r="D32" s="72"/>
@@ -5793,46 +5793,46 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15">
       <c r="A1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" t="s">
         <v>38</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>39</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>40</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>41</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>42</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>43</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>44</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>45</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>46</v>
       </c>
-      <c r="J1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K1" t="s">
-        <v>48</v>
-      </c>
       <c r="L1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="M1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N1" t="s">
-        <v>214</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15">
@@ -5843,31 +5843,31 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G2" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L2">
         <v>0.0342465753424658</v>
@@ -5876,7 +5876,7 @@
         <v>0.0342465753424658</v>
       </c>
       <c r="N2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15">
@@ -5887,31 +5887,31 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>232</v>
+        <v>262</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G3" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L3">
         <v>0.0342465753424658</v>
@@ -5920,7 +5920,7 @@
         <v>0.0342465753424658</v>
       </c>
       <c r="N3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15">
@@ -5931,31 +5931,31 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G4" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L4">
         <v>0.0342465753424658</v>
@@ -5964,7 +5964,7 @@
         <v>0.0342465753424658</v>
       </c>
       <c r="N4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15">
@@ -5975,31 +5975,31 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G5" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L5">
         <v>0.0342465753424658</v>
@@ -6008,7 +6008,7 @@
         <v>0.0342465753424658</v>
       </c>
       <c r="N5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15">
@@ -6016,34 +6016,34 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C6" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F6" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G6" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L6">
         <v>2.7466471585410202</v>
@@ -6052,7 +6052,7 @@
         <v>2.7466471585410202</v>
       </c>
       <c r="N6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15">
@@ -6060,34 +6060,34 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C7" t="s">
-        <v>232</v>
+        <v>262</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F7" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G7" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L7">
         <v>2.7679848891515602</v>
@@ -6096,7 +6096,7 @@
         <v>2.7679848891515602</v>
       </c>
       <c r="N7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15">
@@ -6104,34 +6104,34 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C8" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F8" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G8" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L8">
         <v>2.7466471585410202</v>
@@ -6140,7 +6140,7 @@
         <v>2.7466471585410202</v>
       </c>
       <c r="N8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15">
@@ -6148,34 +6148,34 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C9" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F9" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G9" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L9">
         <v>2.7679848891515602</v>
@@ -6184,7 +6184,7 @@
         <v>2.7679848891515602</v>
       </c>
       <c r="N9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -6204,46 +6204,46 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15">
       <c r="A1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" t="s">
         <v>38</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>39</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>40</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>41</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>42</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>43</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>44</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>45</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>46</v>
       </c>
-      <c r="J1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K1" t="s">
-        <v>48</v>
-      </c>
       <c r="L1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="M1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N1" t="s">
-        <v>214</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15">
@@ -6251,34 +6251,34 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F2" t="s">
         <v>245</v>
       </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
-        <v>215</v>
-      </c>
       <c r="G2" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L2">
         <v>2.4973571887487398</v>
@@ -6287,7 +6287,7 @@
         <v>2.4973571887487398</v>
       </c>
       <c r="N2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15">
@@ -6295,34 +6295,34 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C3" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F3" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G3" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L3">
         <v>4.3260777448279004</v>
@@ -6331,7 +6331,7 @@
         <v>4.3260777448279004</v>
       </c>
       <c r="N3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15">
@@ -6339,34 +6339,34 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C4" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F4" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G4" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -6375,7 +6375,7 @@
         <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15">
@@ -6383,34 +6383,34 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F5" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G5" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -6419,7 +6419,7 @@
         <v>1</v>
       </c>
       <c r="N5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15">
@@ -6427,34 +6427,34 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C6" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F6" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G6" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L6">
         <v>0.48784295359637803</v>
@@ -6463,7 +6463,7 @@
         <v>0.48784295359637803</v>
       </c>
       <c r="N6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15">
@@ -6471,34 +6471,34 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C7" t="s">
-        <v>248</v>
+        <v>197</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F7" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G7" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L7">
         <v>0.37305637627958299</v>
@@ -6507,7 +6507,7 @@
         <v>0.37305637627958299</v>
       </c>
       <c r="N7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15">
@@ -6515,34 +6515,34 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C8" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F8" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G8" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L8">
         <v>0.31709791983764601</v>
@@ -6551,7 +6551,7 @@
         <v>0.31709791983764601</v>
       </c>
       <c r="N8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15">
@@ -6559,34 +6559,34 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C9" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F9" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G9" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L9">
         <v>1.2683916793505801</v>
@@ -6595,7 +6595,7 @@
         <v>1.2683916793505801</v>
       </c>
       <c r="N9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15">
@@ -6603,34 +6603,34 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C10" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F10" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G10" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H10" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I10" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J10" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K10" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L10">
         <v>33.491553664929803</v>
@@ -6639,7 +6639,7 @@
         <v>33.491553664929803</v>
       </c>
       <c r="N10" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15">
@@ -6647,34 +6647,34 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C11" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F11" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G11" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I11" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J11" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K11" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L11">
         <v>58.016156280053501</v>
@@ -6683,7 +6683,7 @@
         <v>58.016156280053501</v>
       </c>
       <c r="N11" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15">
@@ -6691,34 +6691,34 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>255</v>
+        <v>209</v>
       </c>
       <c r="C12" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G12" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L12">
         <v>0.019199999999999998</v>
@@ -6727,7 +6727,7 @@
         <v>0.019199999999999998</v>
       </c>
       <c r="N12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15">
@@ -6735,34 +6735,34 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>255</v>
+        <v>209</v>
       </c>
       <c r="C13" t="s">
-        <v>248</v>
+        <v>197</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G13" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L13">
         <v>0.071999999999999995</v>
@@ -6771,7 +6771,7 @@
         <v>0.071999999999999995</v>
       </c>
       <c r="N13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15">
@@ -6779,34 +6779,34 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>255</v>
+        <v>209</v>
       </c>
       <c r="C14" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G14" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L14">
         <v>0.38400000000000001</v>
@@ -6815,7 +6815,7 @@
         <v>0.38400000000000001</v>
       </c>
       <c r="N14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15">
@@ -6823,34 +6823,34 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>255</v>
+        <v>209</v>
       </c>
       <c r="C15" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G15" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L15">
         <v>0.0047999999999999996</v>
@@ -6859,7 +6859,7 @@
         <v>0.0047999999999999996</v>
       </c>
       <c r="N15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -6885,18 +6885,18 @@
   <sheetData>
     <row r="3" spans="1:3" ht="15">
       <c r="A3" s="22" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18.75">
       <c r="A4" s="24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" s="25"/>
       <c r="C4" s="26"/>
@@ -6912,7 +6912,7 @@
     <row r="6" spans="1:3" ht="15">
       <c r="A6" s="27"/>
       <c r="B6" s="79" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C6" s="80"/>
     </row>
@@ -6921,195 +6921,195 @@
     </row>
     <row r="8" spans="1:3" ht="18.75">
       <c r="A8" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B8" s="29"/>
       <c r="C8" s="15"/>
     </row>
     <row r="9" spans="1:3" ht="15">
       <c r="A9" s="30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" s="32"/>
     </row>
     <row r="10" spans="1:3" ht="15">
       <c r="A10" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="34" t="s">
         <v>52</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>54</v>
       </c>
       <c r="C10" s="35"/>
     </row>
     <row r="11" spans="1:3" ht="15">
       <c r="A11" s="36"/>
       <c r="B11" s="31" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C11" s="36"/>
     </row>
     <row r="14" spans="1:1" ht="21">
       <c r="A14" s="21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15">
       <c r="A15" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="37" t="s">
         <v>57</v>
-      </c>
-      <c r="B15" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="37" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15">
       <c r="A16" s="38" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B16" s="39"/>
       <c r="C16" s="39"/>
     </row>
     <row r="17" spans="1:3" ht="15">
       <c r="A17" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15">
       <c r="A18" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15">
       <c r="A19" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
     </row>
     <row r="20" spans="1:3" ht="15">
       <c r="A20" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15">
       <c r="A21" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15">
       <c r="A22" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15">
       <c r="A23" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
     </row>
     <row r="24" spans="1:3" ht="15">
       <c r="A24" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15">
       <c r="A25" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15">
       <c r="A26" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15">
       <c r="A27" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15">
       <c r="A28" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15">
       <c r="A29" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15">
       <c r="A30" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="15">
       <c r="A31" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15">
       <c r="A32" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15">
@@ -7120,150 +7120,150 @@
         <v>11</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15">
       <c r="A34" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15">
       <c r="A35" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15">
       <c r="A36" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15">
       <c r="A37" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15">
       <c r="A38" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15">
       <c r="A39" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15">
       <c r="A40" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15">
       <c r="A41" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15">
       <c r="A42" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15">
       <c r="A43" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15">
       <c r="A44" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15">
       <c r="A45" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15">
       <c r="A46" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -7295,12 +7295,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="23.25">
       <c r="A1" s="3" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15">
       <c r="A2" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" thickBot="1">
@@ -7317,18 +7317,18 @@
         <v>4</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15">
       <c r="A4" s="9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -7339,14 +7339,14 @@
     </row>
     <row r="5" spans="1:8" ht="15">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1" t="str">
         <f t="shared" si="0" ref="B5">"S-SH-"&amp;F5&amp;"_"&amp;G5&amp;"*"</f>
         <v>S-SH-PU_COA*</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D5" s="7">
         <f>SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,AFA!H5,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"AFA")</f>
@@ -7367,14 +7367,14 @@
     </row>
     <row r="6" spans="1:8" ht="15">
       <c r="A6" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B6" s="1" t="str">
         <f t="shared" si="2" ref="B6:B17">"S-SH-"&amp;F6&amp;"_"&amp;G6&amp;"*"</f>
         <v>S-SH-PU_LPG*</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D6" s="7">
         <f>SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,AFA!H6,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"AFA")</f>
@@ -7395,14 +7395,14 @@
     </row>
     <row r="7" spans="1:8" ht="15">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B7" s="1" t="str">
         <f t="shared" si="2"/>
         <v>S-SH-PU_OIL*</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D7" s="7">
         <f>SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,AFA!H7,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"AFA")</f>
@@ -7423,14 +7423,14 @@
     </row>
     <row r="8" spans="1:8" ht="15">
       <c r="A8" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B8" s="1" t="str">
         <f t="shared" si="2"/>
         <v>S-SH-PU_GAS*</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D8" s="7">
         <f>SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,AFA!H8,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"AFA")</f>
@@ -7451,14 +7451,14 @@
     </row>
     <row r="9" spans="1:8" ht="15">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B9" s="1" t="str">
         <f t="shared" si="2"/>
         <v>S-SH-PU_BIO*</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D9" s="7">
         <f>SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,AFA!H9,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"AFA")</f>
@@ -7479,14 +7479,14 @@
     </row>
     <row r="10" spans="1:8" ht="15">
       <c r="A10" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1" t="str">
         <f>"S-SH-"&amp;F10&amp;"_"&amp;G10&amp;"*, -*N1"</f>
         <v>S-SH-PU_ELC*, -*N1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D10" s="7">
         <f>SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,AFA!H10,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"AFA")</f>
@@ -7507,14 +7507,14 @@
     </row>
     <row r="11" spans="1:8" ht="15">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B11" s="1" t="str">
         <f>"S-SH-"&amp;F11&amp;"_"&amp;G11&amp;"*N1"</f>
         <v>S-SH-PU_ELC*N1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D11" s="7">
         <f>SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,AFA!H11,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"AFA")</f>
@@ -7535,14 +7535,14 @@
     </row>
     <row r="12" spans="1:8" ht="15">
       <c r="A12" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B12" s="4" t="str">
         <f t="shared" si="4" ref="B12:B13">"S-SH-"&amp;F12&amp;"_"&amp;G12&amp;"*"</f>
         <v>S-SH-PU_HET*</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D12" s="8">
         <f>SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,AFA!H12,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"AFA")</f>
@@ -7563,14 +7563,14 @@
     </row>
     <row r="13" spans="1:8" ht="15">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B13" s="1" t="str">
         <f t="shared" si="4"/>
         <v>S-SH-CS_COA*</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D13" s="7">
         <f>SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,AFA!H13,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"AFA")</f>
@@ -7591,14 +7591,14 @@
     </row>
     <row r="14" spans="1:8" ht="15">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1" t="str">
         <f t="shared" si="2"/>
         <v>S-SH-CS_LPG*</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D14" s="7">
         <f>SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,AFA!H14,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"AFA")</f>
@@ -7619,14 +7619,14 @@
     </row>
     <row r="15" spans="1:8" ht="15">
       <c r="A15" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B15" s="1" t="str">
         <f t="shared" si="2"/>
         <v>S-SH-CS_OIL*</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D15" s="7">
         <f>SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,AFA!H15,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"AFA")</f>
@@ -7647,14 +7647,14 @@
     </row>
     <row r="16" spans="1:8" ht="15">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B16" s="1" t="str">
         <f t="shared" si="2"/>
         <v>S-SH-CS_GAS*</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D16" s="7">
         <f>SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,AFA!H16,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"AFA")</f>
@@ -7675,14 +7675,14 @@
     </row>
     <row r="17" spans="1:8" ht="15">
       <c r="A17" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B17" s="1" t="str">
         <f t="shared" si="2"/>
         <v>S-SH-CS_BIO*</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D17" s="7">
         <f>SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,AFA!H17,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"AFA")</f>
@@ -7703,14 +7703,14 @@
     </row>
     <row r="18" spans="1:8" ht="15">
       <c r="A18" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B18" s="1" t="str">
         <f>"S-SH-"&amp;F18&amp;"_"&amp;G18&amp;"*, -*N1"</f>
         <v>S-SH-CS_ELC*, -*N1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D18" s="7">
         <f>SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,AFA!H18,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"AFA")</f>
@@ -7731,14 +7731,14 @@
     </row>
     <row r="19" spans="1:8" ht="15">
       <c r="A19" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B19" s="1" t="str">
         <f>"S-SH-"&amp;F19&amp;"_"&amp;G19&amp;"*N1"</f>
         <v>S-SH-CS_ELC*N1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D19" s="7">
         <f>SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,AFA!H19,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"AFA")</f>
@@ -7759,14 +7759,14 @@
     </row>
     <row r="20" spans="1:8" ht="15.75" thickBot="1">
       <c r="A20" s="12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B20" s="12" t="str">
         <f t="shared" si="7" ref="B20">"S-SH-"&amp;F20&amp;"_"&amp;G20&amp;"*"</f>
         <v>S-SH-CS_HET*</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D20" s="13">
         <f>SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,AFA!H20,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"AFA")</f>
@@ -7787,7 +7787,7 @@
     </row>
     <row r="21" spans="1:8" ht="15">
       <c r="A21" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -7798,7 +7798,7 @@
     </row>
     <row r="22" spans="1:8" ht="15">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="str">
         <f t="shared" si="8" ref="B22">"S-WH-"&amp;F22&amp;"_"&amp;G22&amp;"*"</f>
@@ -7848,7 +7848,7 @@
     </row>
     <row r="24" spans="1:8" ht="15">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B24" s="1" t="str">
         <f t="shared" si="10"/>
@@ -7974,7 +7974,7 @@
     </row>
     <row r="29" spans="1:8" ht="15">
       <c r="A29" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B29" s="1" t="str">
         <f t="shared" si="12" ref="B29">"S-WH-"&amp;F29&amp;"_"&amp;G29&amp;"*"</f>
@@ -8024,7 +8024,7 @@
     </row>
     <row r="31" spans="1:8" ht="15">
       <c r="A31" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B31" s="1" t="str">
         <f t="shared" si="10"/>
@@ -8150,7 +8150,7 @@
     </row>
     <row r="36" spans="1:8" ht="15">
       <c r="A36" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
@@ -8161,14 +8161,14 @@
     </row>
     <row r="37" spans="1:8" ht="15">
       <c r="A37" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B37" s="1" t="str">
         <f t="shared" si="15" ref="B37:B42">"S-SH-"&amp;F37&amp;"_"&amp;G37&amp;"*"</f>
         <v>S-SH-PU_COA*</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D37" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H37,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8189,14 +8189,14 @@
     </row>
     <row r="38" spans="1:8" ht="15">
       <c r="A38" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B38" s="1" t="str">
         <f t="shared" si="15"/>
         <v>S-SH-PU_LPG*</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D38" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H38,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8217,14 +8217,14 @@
     </row>
     <row r="39" spans="1:8" ht="15">
       <c r="A39" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B39" s="1" t="str">
         <f t="shared" si="15"/>
         <v>S-SH-PU_OIL*</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D39" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H39,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8245,14 +8245,14 @@
     </row>
     <row r="40" spans="1:8" ht="15">
       <c r="A40" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B40" s="1" t="str">
         <f t="shared" si="15"/>
         <v>S-SH-PU_GAS*</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D40" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H40,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8273,14 +8273,14 @@
     </row>
     <row r="41" spans="1:8" ht="15">
       <c r="A41" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B41" s="1" t="str">
         <f t="shared" si="15"/>
         <v>S-SH-PU_BIO*</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D41" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H41,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8301,14 +8301,14 @@
     </row>
     <row r="42" spans="1:8" ht="15">
       <c r="A42" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B42" s="1" t="str">
         <f t="shared" si="15"/>
         <v>S-SH-PU_ELC*</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D42" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H42,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8329,14 +8329,14 @@
     </row>
     <row r="43" spans="1:8" ht="15">
       <c r="A43" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B43" s="4" t="str">
         <f t="shared" si="20" ref="B43">"S-SH-"&amp;F43&amp;"_"&amp;G43&amp;"*"</f>
         <v>S-SH-PU_HET*</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D43" s="8">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H43,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8357,14 +8357,14 @@
     </row>
     <row r="44" spans="1:8" ht="15">
       <c r="A44" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B44" s="1" t="str">
         <f t="shared" si="21" ref="B44:B49">"S-SH-"&amp;F44&amp;"_"&amp;G44&amp;"*"</f>
         <v>S-SH-CS_COA*</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D44" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H44,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8385,14 +8385,14 @@
     </row>
     <row r="45" spans="1:8" ht="15">
       <c r="A45" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B45" s="1" t="str">
         <f t="shared" si="21"/>
         <v>S-SH-CS_LPG*</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D45" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H45,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8413,14 +8413,14 @@
     </row>
     <row r="46" spans="1:8" ht="15">
       <c r="A46" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B46" s="1" t="str">
         <f t="shared" si="21"/>
         <v>S-SH-CS_OIL*</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D46" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H46,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8441,14 +8441,14 @@
     </row>
     <row r="47" spans="1:8" ht="15">
       <c r="A47" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B47" s="1" t="str">
         <f t="shared" si="21"/>
         <v>S-SH-CS_GAS*</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D47" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H47,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8469,14 +8469,14 @@
     </row>
     <row r="48" spans="1:8" ht="15">
       <c r="A48" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B48" s="1" t="str">
         <f t="shared" si="21"/>
         <v>S-SH-CS_BIO*</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D48" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H48,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8497,14 +8497,14 @@
     </row>
     <row r="49" spans="1:8" ht="15">
       <c r="A49" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B49" s="1" t="str">
         <f t="shared" si="21"/>
         <v>S-SH-CS_ELC*</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D49" s="7">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H49,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8525,14 +8525,14 @@
     </row>
     <row r="50" spans="1:8" ht="15.75" thickBot="1">
       <c r="A50" s="12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B50" s="12" t="str">
         <f t="shared" si="23" ref="B50">"S-SH-"&amp;F50&amp;"_"&amp;G50&amp;"*"</f>
         <v>S-SH-CS_HET*</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D50" s="13">
         <f>SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,AFA!H50,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"AFA")</f>
@@ -8553,7 +8553,7 @@
     </row>
     <row r="51" spans="1:8" ht="15">
       <c r="A51" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B51" s="10"/>
       <c r="C51" s="10"/>
@@ -8613,7 +8613,7 @@
     </row>
     <row r="54" spans="1:8" ht="15">
       <c r="A54" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B54" s="10"/>
       <c r="C54" s="10"/>
@@ -8624,14 +8624,14 @@
     </row>
     <row r="55" spans="1:8" ht="15">
       <c r="A55" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B55" s="1" t="str">
         <f t="shared" si="24" ref="B55:B56">"S-SH-"&amp;F55&amp;"_"&amp;G55&amp;"*"</f>
         <v>S-SH-PU_ELC*</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="D55" s="7">
         <f>SUMIFS('BY_S-SC'!$L$2:$L$100,'BY_S-SC'!$C$2:$C$100,AFA!H55,'BY_S-SC'!$A$2:$A$100,"BASE",'BY_S-SC'!$B$2:$B$100,"AFA")</f>
@@ -8651,14 +8651,14 @@
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1">
       <c r="A56" s="12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B56" s="12" t="str">
         <f t="shared" si="24"/>
         <v>S-SH-CS_ELC*</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="D56" s="13">
         <f>SUMIFS('BY_S-SC'!$L$2:$L$100,'BY_S-SC'!$C$2:$C$100,AFA!H56,'BY_S-SC'!$A$2:$A$100,"BASE",'BY_S-SC'!$B$2:$B$100,"AFA")</f>
@@ -8702,12 +8702,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="23.25">
       <c r="A1" s="3" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15">
       <c r="A2" s="6" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" thickBot="1">
@@ -8724,18 +8724,18 @@
         <v>4</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15">
       <c r="A4" s="9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -8746,14 +8746,14 @@
     </row>
     <row r="5" spans="1:8" ht="15">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1" t="str">
         <f t="shared" si="0" ref="B5:B17">"S-SH-"&amp;F5&amp;"_"&amp;G5&amp;"*"</f>
         <v>S-SH-PU_COA*</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D5" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,EFF!H5,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"EFF")</f>
@@ -8774,14 +8774,14 @@
     </row>
     <row r="6" spans="1:8" ht="15">
       <c r="A6" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B6" s="1" t="str">
         <f t="shared" si="0"/>
         <v>S-SH-PU_LPG*</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D6" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,EFF!H6,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"EFF")</f>
@@ -8802,14 +8802,14 @@
     </row>
     <row r="7" spans="1:8" ht="15">
       <c r="A7" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B7" s="1" t="str">
         <f t="shared" si="0"/>
         <v>S-SH-PU_OIL*</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D7" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,EFF!H7,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"EFF")</f>
@@ -8830,14 +8830,14 @@
     </row>
     <row r="8" spans="1:8" ht="15">
       <c r="A8" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B8" s="1" t="str">
         <f t="shared" si="0"/>
         <v>S-SH-PU_GAS*</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D8" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,EFF!H8,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"EFF")</f>
@@ -8858,14 +8858,14 @@
     </row>
     <row r="9" spans="1:8" ht="15">
       <c r="A9" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B9" s="1" t="str">
         <f t="shared" si="0"/>
         <v>S-SH-PU_BIO*</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D9" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,EFF!H9,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"EFF")</f>
@@ -8886,14 +8886,14 @@
     </row>
     <row r="10" spans="1:8" ht="15">
       <c r="A10" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B10" s="1" t="str">
         <f>"S-SH-"&amp;F10&amp;"_"&amp;G10&amp;"*, -*N1"</f>
         <v>S-SH-PU_ELC*, -*N1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D10" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,EFF!H10,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"EFF")</f>
@@ -8914,14 +8914,14 @@
     </row>
     <row r="11" spans="1:8" ht="15">
       <c r="A11" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B11" s="1" t="str">
         <f>"S-SH-"&amp;F11&amp;"_"&amp;G11&amp;"*N1"</f>
         <v>S-SH-PU_ELC*N1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D11" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,EFF!H11,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"EFF")</f>
@@ -8942,14 +8942,14 @@
     </row>
     <row r="12" spans="1:8" ht="15">
       <c r="A12" s="4" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B12" s="4" t="str">
         <f t="shared" si="2" ref="B12:B13">"S-SH-"&amp;F12&amp;"_"&amp;G12&amp;"*"</f>
         <v>S-SH-PU_HET*</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D12" s="8" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,EFF!H12,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"EFF")</f>
@@ -8970,14 +8970,14 @@
     </row>
     <row r="13" spans="1:8" ht="15">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B13" s="1" t="str">
         <f t="shared" si="2"/>
         <v>S-SH-CS_COA*</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D13" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,EFF!H13,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"EFF")</f>
@@ -8998,14 +8998,14 @@
     </row>
     <row r="14" spans="1:8" ht="15">
       <c r="A14" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B14" s="1" t="str">
         <f t="shared" si="0"/>
         <v>S-SH-CS_LPG*</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D14" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,EFF!H14,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"EFF")</f>
@@ -9026,14 +9026,14 @@
     </row>
     <row r="15" spans="1:8" ht="15">
       <c r="A15" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B15" s="1" t="str">
         <f t="shared" si="0"/>
         <v>S-SH-CS_OIL*</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D15" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,EFF!H15,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"EFF")</f>
@@ -9054,14 +9054,14 @@
     </row>
     <row r="16" spans="1:8" ht="15">
       <c r="A16" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B16" s="1" t="str">
         <f t="shared" si="0"/>
         <v>S-SH-CS_GAS*</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D16" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,EFF!H16,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"EFF")</f>
@@ -9082,14 +9082,14 @@
     </row>
     <row r="17" spans="1:8" ht="15">
       <c r="A17" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B17" s="1" t="str">
         <f t="shared" si="0"/>
         <v>S-SH-CS_BIO*</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D17" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,EFF!H17,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"EFF")</f>
@@ -9110,14 +9110,14 @@
     </row>
     <row r="18" spans="1:8" ht="15">
       <c r="A18" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B18" s="1" t="str">
         <f>"S-SH-"&amp;F18&amp;"_"&amp;G18&amp;"*, -*N1"</f>
         <v>S-SH-CS_ELC*, -*N1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D18" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,EFF!H18,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"EFF")</f>
@@ -9138,14 +9138,14 @@
     </row>
     <row r="19" spans="1:8" ht="15">
       <c r="A19" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B19" s="1" t="str">
         <f>"S-SH-"&amp;F19&amp;"_"&amp;G19&amp;"*N1"</f>
         <v>S-SH-CS_ELC*N1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D19" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,EFF!H19,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"EFF")</f>
@@ -9166,14 +9166,14 @@
     </row>
     <row r="20" spans="1:8" ht="15.75" thickBot="1">
       <c r="A20" s="12" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B20" s="12" t="str">
         <f t="shared" si="5" ref="B20">"S-SH-"&amp;F20&amp;"_"&amp;G20&amp;"*"</f>
         <v>S-SH-CS_HET*</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D20" s="13" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,EFF!H20,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"EFF")</f>
@@ -9194,7 +9194,7 @@
     </row>
     <row r="21" spans="1:8" ht="15">
       <c r="A21" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -9205,14 +9205,14 @@
     </row>
     <row r="22" spans="1:8" ht="15">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="str">
         <f t="shared" si="6" ref="B22:B35">"S-WH-"&amp;F22&amp;"_"&amp;G22&amp;"*"</f>
         <v>S-WH-PU_COA*</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D22" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H22,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9233,14 +9233,14 @@
     </row>
     <row r="23" spans="1:8" ht="15">
       <c r="A23" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B23" s="1" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-PU_LPG*</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D23" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H23,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9261,14 +9261,14 @@
     </row>
     <row r="24" spans="1:8" ht="15">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B24" s="1" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-PU_OIL*</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D24" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H24,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9289,14 +9289,14 @@
     </row>
     <row r="25" spans="1:8" ht="15">
       <c r="A25" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B25" s="1" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-PU_GAS*</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D25" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H25,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9317,14 +9317,14 @@
     </row>
     <row r="26" spans="1:8" ht="15">
       <c r="A26" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B26" s="1" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-PU_BIO*</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D26" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H26,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9345,14 +9345,14 @@
     </row>
     <row r="27" spans="1:8" ht="15">
       <c r="A27" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B27" s="1" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-PU_SOL*</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D27" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H27,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9373,14 +9373,14 @@
     </row>
     <row r="28" spans="1:8" ht="15">
       <c r="A28" s="4" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B28" s="4" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-PU_ELC*</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D28" s="8" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H28,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9401,14 +9401,14 @@
     </row>
     <row r="29" spans="1:8" ht="15">
       <c r="A29" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B29" s="1" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-CS_COA*</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D29" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H29,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9429,14 +9429,14 @@
     </row>
     <row r="30" spans="1:8" ht="15">
       <c r="A30" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B30" s="1" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-CS_LPG*</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D30" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H30,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9457,14 +9457,14 @@
     </row>
     <row r="31" spans="1:8" ht="15">
       <c r="A31" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B31" s="1" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-CS_OIL*</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D31" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H31,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9485,14 +9485,14 @@
     </row>
     <row r="32" spans="1:8" ht="15">
       <c r="A32" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B32" s="1" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-CS_GAS*</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D32" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H32,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9513,14 +9513,14 @@
     </row>
     <row r="33" spans="1:8" ht="15">
       <c r="A33" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B33" s="1" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-CS_BIO*</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D33" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H33,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9541,14 +9541,14 @@
     </row>
     <row r="34" spans="1:8" ht="15">
       <c r="A34" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B34" s="1" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-CS_SOL*</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D34" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H34,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9569,14 +9569,14 @@
     </row>
     <row r="35" spans="1:8" ht="15">
       <c r="A35" s="4" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B35" s="4" t="str">
         <f t="shared" si="6"/>
         <v>S-WH-CS_ELC*</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D35" s="8" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H35,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9597,7 +9597,7 @@
     </row>
     <row r="36" spans="1:8" ht="15">
       <c r="A36" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
@@ -9608,14 +9608,14 @@
     </row>
     <row r="37" spans="1:8" ht="15">
       <c r="A37" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B37" s="1" t="str">
         <f t="shared" si="9" ref="B37:B49">"S-SH-"&amp;F37&amp;"_"&amp;G37&amp;"*"</f>
         <v>S-SH-PU_COA*</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D37" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H37,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9636,14 +9636,14 @@
     </row>
     <row r="38" spans="1:8" ht="15">
       <c r="A38" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B38" s="1" t="str">
         <f t="shared" si="9"/>
         <v>S-SH-PU_LPG*</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D38" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H38,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9664,14 +9664,14 @@
     </row>
     <row r="39" spans="1:8" ht="15">
       <c r="A39" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B39" s="1" t="str">
         <f t="shared" si="9"/>
         <v>S-SH-PU_OIL*</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D39" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H39,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9692,14 +9692,14 @@
     </row>
     <row r="40" spans="1:8" ht="15">
       <c r="A40" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B40" s="1" t="str">
         <f t="shared" si="9"/>
         <v>S-SH-PU_GAS*</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D40" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H40,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9720,14 +9720,14 @@
     </row>
     <row r="41" spans="1:8" ht="15">
       <c r="A41" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B41" s="1" t="str">
         <f t="shared" si="9"/>
         <v>S-SH-PU_BIO*</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D41" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H41,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9748,14 +9748,14 @@
     </row>
     <row r="42" spans="1:8" ht="15">
       <c r="A42" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B42" s="1" t="str">
         <f t="shared" si="9"/>
         <v>S-SH-PU_ELC*</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D42" s="58" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,EFF!H42,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"EFF")</f>
@@ -9776,14 +9776,14 @@
     </row>
     <row r="43" spans="1:8" ht="15">
       <c r="A43" s="4" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B43" s="4" t="str">
         <f t="shared" si="11" ref="B43">"S-SH-"&amp;F43&amp;"_"&amp;G43&amp;"*"</f>
         <v>S-SH-PU_HET*</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="D43" s="8" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H43,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9804,14 +9804,14 @@
     </row>
     <row r="44" spans="1:8" ht="15">
       <c r="A44" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B44" s="1" t="str">
         <f t="shared" si="9"/>
         <v>S-SH-CS_COA*</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D44" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H44,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9832,14 +9832,14 @@
     </row>
     <row r="45" spans="1:8" ht="15">
       <c r="A45" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B45" s="1" t="str">
         <f t="shared" si="9"/>
         <v>S-SH-CS_LPG*</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D45" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H45,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9860,14 +9860,14 @@
     </row>
     <row r="46" spans="1:8" ht="15">
       <c r="A46" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B46" s="1" t="str">
         <f t="shared" si="9"/>
         <v>S-SH-CS_OIL*</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D46" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H46,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9888,14 +9888,14 @@
     </row>
     <row r="47" spans="1:8" ht="15">
       <c r="A47" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B47" s="1" t="str">
         <f t="shared" si="9"/>
         <v>S-SH-CS_GAS*</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D47" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H47,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9916,14 +9916,14 @@
     </row>
     <row r="48" spans="1:8" ht="15">
       <c r="A48" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B48" s="1" t="str">
         <f t="shared" si="9"/>
         <v>S-SH-CS_BIO*</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D48" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H48,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -9944,14 +9944,14 @@
     </row>
     <row r="49" spans="1:8" ht="15">
       <c r="A49" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B49" s="1" t="str">
         <f t="shared" si="9"/>
         <v>S-SH-CS_ELC*</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D49" s="58" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SH'!$L$2:$L$100,'BY_S-SH'!$C$2:$C$100,EFF!H49,'BY_S-SH'!$A$2:$A$100,"BASE",'BY_S-SH'!$B$2:$B$100,"EFF")</f>
@@ -9972,14 +9972,14 @@
     </row>
     <row r="50" spans="1:8" ht="15.75" thickBot="1">
       <c r="A50" s="12" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B50" s="12" t="str">
         <f t="shared" si="13" ref="B50">"S-SH-"&amp;F50&amp;"_"&amp;G50&amp;"*"</f>
         <v>S-SH-CS_HET*</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D50" s="13" t="str">
         <f>"*"&amp;SUMIFS('BY_S-WH'!$L$2:$L$100,'BY_S-WH'!$C$2:$C$100,EFF!H50,'BY_S-WH'!$A$2:$A$100,"BASE",'BY_S-WH'!$B$2:$B$100,"EFF")</f>
@@ -10000,7 +10000,7 @@
     </row>
     <row r="51" spans="1:8" ht="15">
       <c r="A51" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B51" s="10"/>
       <c r="C51" s="10"/>
@@ -10011,14 +10011,14 @@
     </row>
     <row r="52" spans="1:8" ht="15">
       <c r="A52" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B52" s="1" t="str">
         <f>"S-SC-"&amp;F52&amp;"_"&amp;G52&amp;"*"</f>
         <v>S-SC-PU_ELC*</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="D52" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SC'!$L$2:$L$100,'BY_S-SC'!$C$2:$C$100,EFF!H52,'BY_S-SC'!$A$2:$A$100,"BASE",'BY_S-SC'!$B$2:$B$100,"EFF")</f>
@@ -10038,14 +10038,14 @@
     </row>
     <row r="53" spans="1:8" ht="15">
       <c r="A53" s="4" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B53" s="4" t="str">
         <f>"S-SC-"&amp;F53&amp;"_"&amp;G53&amp;"*"</f>
         <v>S-SC-CS_ELC*</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="D53" s="8" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SC'!$L$2:$L$100,'BY_S-SC'!$C$2:$C$100,EFF!H53,'BY_S-SC'!$A$2:$A$100,"BASE",'BY_S-SC'!$B$2:$B$100,"EFF")</f>
@@ -10065,7 +10065,7 @@
     </row>
     <row r="54" spans="1:8" ht="15">
       <c r="A54" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B54" s="10"/>
       <c r="C54" s="10"/>
@@ -10076,14 +10076,14 @@
     </row>
     <row r="55" spans="1:8" ht="15">
       <c r="A55" s="1" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B55" s="1" t="str">
         <f t="shared" si="14" ref="B55:B56">"S-SH-"&amp;F55&amp;"_"&amp;G55&amp;"*"</f>
         <v>S-SH-PU_ELC*</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="D55" s="7" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SC'!$L$2:$L$100,'BY_S-SC'!$C$2:$C$100,EFF!H55,'BY_S-SC'!$A$2:$A$100,"BASE",'BY_S-SC'!$B$2:$B$100,"EFF")</f>
@@ -10103,14 +10103,14 @@
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1">
       <c r="A56" s="12" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="B56" s="12" t="str">
         <f t="shared" si="14"/>
         <v>S-SH-CS_ELC*</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="D56" s="13" t="str">
         <f>"*"&amp;SUMIFS('BY_S-SC'!$L$2:$L$100,'BY_S-SC'!$C$2:$C$100,EFF!H56,'BY_S-SC'!$A$2:$A$100,"BASE",'BY_S-SC'!$B$2:$B$100,"EFF")</f>
@@ -10130,7 +10130,7 @@
     </row>
     <row r="57" spans="1:8" ht="15">
       <c r="A57" s="9" t="s">
-        <v>254</v>
+        <v>208</v>
       </c>
       <c r="B57" s="10"/>
       <c r="C57" s="10"/>
@@ -10141,7 +10141,7 @@
     </row>
     <row r="58" spans="1:8" ht="15">
       <c r="A58" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B58" s="1" t="str">
         <f t="shared" si="15" ref="B58:B63">"S-"&amp;G58&amp;"-"&amp;F58&amp;"*"</f>
@@ -10166,7 +10166,7 @@
     </row>
     <row r="59" spans="1:8" ht="15">
       <c r="A59" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B59" s="1" t="str">
         <f t="shared" si="15"/>
@@ -10191,7 +10191,7 @@
     </row>
     <row r="60" spans="1:8" ht="15">
       <c r="A60" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B60" s="1" t="str">
         <f t="shared" si="15"/>
@@ -10216,7 +10216,7 @@
     </row>
     <row r="61" spans="1:8" ht="15">
       <c r="A61" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B61" s="1" t="str">
         <f t="shared" si="15"/>
@@ -10241,7 +10241,7 @@
     </row>
     <row r="62" spans="1:13" ht="15">
       <c r="A62" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B62" s="1" t="str">
         <f t="shared" si="15"/>
@@ -10267,12 +10267,12 @@
       <c r="K62" s="54"/>
       <c r="L62" s="54"/>
       <c r="M62" s="55" t="s">
-        <v>257</v>
+        <v>211</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="15">
       <c r="A63" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B63" s="1" t="str">
         <f t="shared" si="15"/>
@@ -10313,7 +10313,7 @@
     </row>
     <row r="64" spans="1:13" ht="15">
       <c r="A64" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B64" s="1" t="str">
         <f>"S-"&amp;G64&amp;"-"&amp;F64&amp;"*N1"</f>
@@ -10354,7 +10354,7 @@
     </row>
     <row r="65" spans="1:13" ht="15.75" thickBot="1">
       <c r="A65" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B65" s="12" t="str">
         <f>"S-"&amp;G65&amp;"-"&amp;F65&amp;"*N2"</f>
@@ -10396,7 +10396,7 @@
     </row>
     <row r="66" spans="1:13" ht="15">
       <c r="A66" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J66" s="54" t="str">
         <f>Legend!$C$18</f>
@@ -10417,7 +10417,7 @@
     </row>
     <row r="67" spans="1:1" ht="15">
       <c r="A67" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -10454,7 +10454,7 @@
     </row>
     <row r="3" spans="2:10" ht="15">
       <c r="B3" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="G5" s="20"/>
       <c r="H5" s="20" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I5" s="20"/>
       <c r="J5" s="20"/>
@@ -10521,7 +10521,7 @@
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E6" s="18">
         <v>2018</v>
@@ -10531,7 +10531,7 @@
       </c>
       <c r="G6" s="20"/>
       <c r="H6" s="20" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I6" s="20"/>
       <c r="J6" s="20"/>
@@ -10539,7 +10539,7 @@
     <row r="7" s="0" customFormat="1" ht="15"/>
     <row r="8" spans="2:10" ht="15">
       <c r="B8" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="G10" s="20"/>
       <c r="H10" s="20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I10" s="20"/>
       <c r="J10" s="20"/>
@@ -10606,7 +10606,7 @@
       </c>
       <c r="C11" s="18"/>
       <c r="D11" s="23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E11" s="18">
         <v>2018</v>
@@ -10616,7 +10616,7 @@
       </c>
       <c r="G11" s="20"/>
       <c r="H11" s="20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I11" s="20"/>
       <c r="J11" s="20"/>
@@ -10624,7 +10624,7 @@
     <row r="12" s="0" customFormat="1" ht="15"/>
     <row r="13" spans="2:10" ht="15">
       <c r="B13" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -10680,7 +10680,7 @@
       </c>
       <c r="G15" s="20"/>
       <c r="H15" s="20" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I15" s="20"/>
       <c r="J15" s="20"/>
@@ -10691,7 +10691,7 @@
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E16" s="18">
         <v>2018</v>
@@ -10701,14 +10701,14 @@
       </c>
       <c r="G16" s="20"/>
       <c r="H16" s="20" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I16" s="20"/>
       <c r="J16" s="20"/>
     </row>
     <row r="18" spans="2:10" ht="15">
       <c r="B18" s="6" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="C20" s="18"/>
       <c r="D20" s="23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E20" s="18">
         <v>2018</v>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="G20" s="20"/>
       <c r="H20" s="20" t="s">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="I20" s="20"/>
       <c r="J20" s="20"/>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="C21" s="18"/>
       <c r="D21" s="23" t="s">
-        <v>255</v>
+        <v>209</v>
       </c>
       <c r="E21" s="18">
         <v>2018</v>
@@ -10785,7 +10785,7 @@
       </c>
       <c r="G21" s="20"/>
       <c r="H21" s="20" t="s">
-        <v>256</v>
+        <v>210</v>
       </c>
       <c r="I21" s="20"/>
       <c r="J21" s="20"/>
@@ -10951,13 +10951,13 @@
     </row>
     <row r="5" spans="1:30" ht="15">
       <c r="A5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" s="42" t="s">
         <v>128</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>129</v>
-      </c>
-      <c r="D5" s="42" t="s">
-        <v>130</v>
       </c>
       <c r="E5" s="41" t="str">
         <f>Regions!A11</f>
@@ -11066,7 +11066,7 @@
     </row>
     <row r="6" spans="1:30" ht="15">
       <c r="A6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C6" s="41" t="str">
         <f>C5</f>
@@ -11183,7 +11183,7 @@
     </row>
     <row r="7" spans="1:30" ht="15">
       <c r="A7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C7" s="41" t="str">
         <f>"*"&amp;C5</f>
@@ -11300,223 +11300,223 @@
     </row>
     <row r="10" spans="1:2" ht="15.75" thickBot="1">
       <c r="A10" s="43" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15">
       <c r="A11" s="44" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B11" s="44" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15">
       <c r="A12" s="45" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15">
       <c r="A13" s="45" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B13" s="45" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15">
       <c r="A14" s="45" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15">
       <c r="A15" s="45" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B15" s="45" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15">
       <c r="A16" s="45" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B16" s="45" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15">
       <c r="A17" s="45" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B17" s="45" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15">
       <c r="A18" s="45" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B18" s="45" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15">
       <c r="A19" s="45" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B19" s="45" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15">
       <c r="A20" s="45" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B20" s="45" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15">
       <c r="A21" s="45" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B21" s="45" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15">
       <c r="A22" s="45" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15">
       <c r="A23" s="45" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15">
       <c r="A24" s="45" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B24" s="45" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15">
       <c r="A25" s="45" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B25" s="45" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15">
       <c r="A26" s="45" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B26" s="45" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15">
       <c r="A27" s="45" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B27" s="45" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15">
       <c r="A28" s="45" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B28" s="45" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="15">
       <c r="A29" s="45" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B29" s="45" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="15">
       <c r="A30" s="45" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B30" s="45" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="15">
       <c r="A31" s="45" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B31" s="45" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="15">
       <c r="A32" s="45" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B32" s="45" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15">
       <c r="A33" s="45" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B33" s="45" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="15">
       <c r="A34" s="45" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B34" s="45" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15">
       <c r="A35" s="45" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B35" s="45" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="15">
       <c r="A36" s="45" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B36" s="45" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="15">
       <c r="A37" s="46" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -11591,7 +11591,7 @@
   <sheetData>
     <row r="3" spans="2:27" ht="15">
       <c r="B3" s="47" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I3" s="49"/>
       <c r="J3"/>
@@ -11615,22 +11615,22 @@
     </row>
     <row r="4" spans="2:27" ht="15.75" thickBot="1">
       <c r="B4" s="50" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C4" s="50" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="50" t="s">
+        <v>188</v>
+      </c>
+      <c r="E4" s="50" t="s">
+        <v>189</v>
+      </c>
+      <c r="F4" s="51" t="s">
         <v>190</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="G4" s="51" t="s">
         <v>191</v>
-      </c>
-      <c r="F4" s="51" t="s">
-        <v>192</v>
-      </c>
-      <c r="G4" s="51" t="s">
-        <v>193</v>
       </c>
       <c r="H4" s="51" t="str">
         <f>Regions!C3</f>
@@ -11661,7 +11661,7 @@
     </row>
     <row r="5" spans="3:27" ht="15">
       <c r="C5" s="53" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -11749,46 +11749,46 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15">
       <c r="A1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" t="s">
         <v>38</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>39</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>40</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>41</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>42</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>43</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>44</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>45</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>46</v>
       </c>
-      <c r="J1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K1" t="s">
-        <v>48</v>
-      </c>
       <c r="L1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="M1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N1" t="s">
-        <v>214</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15">
@@ -11799,31 +11799,31 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G2" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L2">
         <v>0.114155251141553</v>
@@ -11832,7 +11832,7 @@
         <v>0.114155251141553</v>
       </c>
       <c r="N2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15">
@@ -11843,31 +11843,31 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G3" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L3">
         <v>0.114155251141553</v>
@@ -11876,7 +11876,7 @@
         <v>0.114155251141553</v>
       </c>
       <c r="N3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15">
@@ -11887,31 +11887,31 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G4" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L4">
         <v>0.114155251141553</v>
@@ -11920,7 +11920,7 @@
         <v>0.114155251141553</v>
       </c>
       <c r="N4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15">
@@ -11931,31 +11931,31 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G5" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L5">
         <v>0.114155251141553</v>
@@ -11964,7 +11964,7 @@
         <v>0.114155251141553</v>
       </c>
       <c r="N5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15">
@@ -11975,31 +11975,31 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G6" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L6">
         <v>0.114155251141553</v>
@@ -12008,7 +12008,7 @@
         <v>0.114155251141553</v>
       </c>
       <c r="N6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15">
@@ -12019,31 +12019,31 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G7" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L7">
         <v>0.114155251141553</v>
@@ -12052,7 +12052,7 @@
         <v>0.114155251141553</v>
       </c>
       <c r="N7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15">
@@ -12063,31 +12063,31 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G8" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L8">
         <v>0.116438356164384</v>
@@ -12096,7 +12096,7 @@
         <v>0.116438356164384</v>
       </c>
       <c r="N8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15">
@@ -12107,31 +12107,31 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G9" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L9">
         <v>0.114155251141553</v>
@@ -12140,7 +12140,7 @@
         <v>0.114155251141553</v>
       </c>
       <c r="N9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15">
@@ -12151,31 +12151,31 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G10" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H10" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I10" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J10" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K10" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L10">
         <v>0.114155251141553</v>
@@ -12184,7 +12184,7 @@
         <v>0.114155251141553</v>
       </c>
       <c r="N10" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15">
@@ -12195,31 +12195,31 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G11" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I11" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J11" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K11" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L11">
         <v>0.114155251141553</v>
@@ -12228,7 +12228,7 @@
         <v>0.114155251141553</v>
       </c>
       <c r="N11" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15">
@@ -12239,31 +12239,31 @@
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G12" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L12">
         <v>0.114155251141553</v>
@@ -12272,7 +12272,7 @@
         <v>0.114155251141553</v>
       </c>
       <c r="N12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15">
@@ -12283,31 +12283,31 @@
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G13" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L13">
         <v>0.114155251141553</v>
@@ -12316,7 +12316,7 @@
         <v>0.114155251141553</v>
       </c>
       <c r="N13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15">
@@ -12327,31 +12327,31 @@
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G14" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L14">
         <v>0.114155251141553</v>
@@ -12360,7 +12360,7 @@
         <v>0.114155251141553</v>
       </c>
       <c r="N14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15">
@@ -12371,31 +12371,31 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G15" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L15">
         <v>0.114155251141553</v>
@@ -12404,7 +12404,7 @@
         <v>0.114155251141553</v>
       </c>
       <c r="N15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15">
@@ -12415,31 +12415,31 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>273</v>
+        <v>230</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G16" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H16" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I16" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J16" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K16" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L16">
         <v>0.114155251141553</v>
@@ -12448,7 +12448,7 @@
         <v>0.114155251141553</v>
       </c>
       <c r="N16" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15">
@@ -12462,28 +12462,28 @@
         <v>274</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F17" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G17" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H17" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I17" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J17" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K17" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L17">
         <v>0.114155251141553</v>
@@ -12492,7 +12492,7 @@
         <v>0.114155251141553</v>
       </c>
       <c r="N17" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15">
@@ -12500,34 +12500,34 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C18" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F18" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G18" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H18" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I18" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J18" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K18" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L18">
         <v>0.63490443337371305</v>
@@ -12536,7 +12536,7 @@
         <v>0.63490443337371305</v>
       </c>
       <c r="N18" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15">
@@ -12544,34 +12544,34 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C19" t="s">
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F19" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G19" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H19" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I19" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J19" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K19" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L19">
         <v>0.33000000000000002</v>
@@ -12580,7 +12580,7 @@
         <v>0.33000000000000002</v>
       </c>
       <c r="N19" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15">
@@ -12588,34 +12588,34 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C20" t="s">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="D20" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F20" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G20" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H20" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I20" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J20" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K20" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L20">
         <v>2.1000000000000001</v>
@@ -12624,7 +12624,7 @@
         <v>2.1000000000000001</v>
       </c>
       <c r="N20" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="15">
@@ -12632,34 +12632,34 @@
         <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C21" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F21" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G21" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H21" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I21" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J21" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K21" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L21">
         <v>0.81595511259153497</v>
@@ -12668,7 +12668,7 @@
         <v>0.81595511259153497</v>
       </c>
       <c r="N21" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15">
@@ -12676,34 +12676,34 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C22" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F22" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G22" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H22" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I22" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J22" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K22" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L22">
         <v>0.77299617086321304</v>
@@ -12712,7 +12712,7 @@
         <v>0.77299617086321304</v>
       </c>
       <c r="N22" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="15">
@@ -12720,34 +12720,34 @@
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C23" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F23" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G23" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H23" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I23" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J23" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K23" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L23">
         <v>0.33000000000000002</v>
@@ -12756,7 +12756,7 @@
         <v>0.33000000000000002</v>
       </c>
       <c r="N23" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="15">
@@ -12764,34 +12764,34 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C24" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F24" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G24" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H24" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I24" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J24" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K24" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L24">
         <v>0.65835584489725196</v>
@@ -12800,7 +12800,7 @@
         <v>0.65835584489725196</v>
       </c>
       <c r="N24" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="15">
@@ -12808,34 +12808,34 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C25" t="s">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="D25" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F25" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G25" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H25" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I25" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J25" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K25" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L25">
         <v>0.33000000000000002</v>
@@ -12844,7 +12844,7 @@
         <v>0.33000000000000002</v>
       </c>
       <c r="N25" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15">
@@ -12852,34 +12852,34 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C26" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="D26" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F26" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G26" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H26" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I26" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J26" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K26" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L26">
         <v>0.63490443337371305</v>
@@ -12888,7 +12888,7 @@
         <v>0.63490443337371305</v>
       </c>
       <c r="N26" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="15">
@@ -12896,34 +12896,34 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C27" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="D27" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E27" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F27" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G27" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H27" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I27" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J27" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K27" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L27">
         <v>0.33000000000000002</v>
@@ -12932,7 +12932,7 @@
         <v>0.33000000000000002</v>
       </c>
       <c r="N27" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="15">
@@ -12940,34 +12940,34 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="D28" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F28" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G28" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H28" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I28" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J28" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K28" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L28">
         <v>2.1000000000000001</v>
@@ -12976,7 +12976,7 @@
         <v>2.1000000000000001</v>
       </c>
       <c r="N28" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="15">
@@ -12984,34 +12984,34 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C29" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F29" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G29" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H29" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I29" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J29" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K29" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L29">
         <v>0.81595511259153497</v>
@@ -13020,7 +13020,7 @@
         <v>0.81595511259153497</v>
       </c>
       <c r="N29" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="15">
@@ -13028,34 +13028,34 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C30" t="s">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="D30" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F30" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G30" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H30" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I30" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J30" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K30" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L30">
         <v>0.77299617086321304</v>
@@ -13064,7 +13064,7 @@
         <v>0.77299617086321304</v>
       </c>
       <c r="N30" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="15">
@@ -13072,34 +13072,34 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C31" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E31" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F31" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G31" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H31" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I31" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J31" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K31" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L31">
         <v>0.33000000000000002</v>
@@ -13108,7 +13108,7 @@
         <v>0.33000000000000002</v>
       </c>
       <c r="N31" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="15">
@@ -13116,34 +13116,34 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C32" t="s">
-        <v>273</v>
+        <v>230</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F32" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G32" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H32" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I32" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J32" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K32" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L32">
         <v>0.65835584489725196</v>
@@ -13152,7 +13152,7 @@
         <v>0.65835584489725196</v>
       </c>
       <c r="N32" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15">
@@ -13160,34 +13160,34 @@
         <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s">
         <v>274</v>
       </c>
       <c r="D33" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F33" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G33" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H33" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I33" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J33" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K33" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L33">
         <v>0.33000000000000002</v>
@@ -13196,7 +13196,7 @@
         <v>0.33000000000000002</v>
       </c>
       <c r="N33" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -13216,46 +13216,46 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15">
       <c r="A1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" t="s">
         <v>38</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>39</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>40</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>41</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>42</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>43</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>44</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>45</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>46</v>
       </c>
-      <c r="J1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K1" t="s">
-        <v>48</v>
-      </c>
       <c r="L1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="M1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N1" t="s">
-        <v>214</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15">
@@ -13266,31 +13266,31 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F2" t="s">
+        <v>227</v>
+      </c>
+      <c r="G2" t="s">
         <v>229</v>
       </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" t="s">
-        <v>213</v>
-      </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L2">
         <v>0.022831050228310501</v>
@@ -13299,7 +13299,7 @@
         <v>0.022831050228310501</v>
       </c>
       <c r="N2" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15">
@@ -13310,31 +13310,31 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D3" t="s">
+        <v>227</v>
+      </c>
+      <c r="E3" t="s">
         <v>228</v>
       </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G3" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L3">
         <v>0.022831050228310501</v>
@@ -13343,7 +13343,7 @@
         <v>0.022831050228310501</v>
       </c>
       <c r="N3" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15">
@@ -13354,31 +13354,31 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G4" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L4">
         <v>0.022831050228310501</v>
@@ -13387,7 +13387,7 @@
         <v>0.022831050228310501</v>
       </c>
       <c r="N4" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15">
@@ -13398,31 +13398,31 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G5" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L5">
         <v>0.022831050228310501</v>
@@ -13431,7 +13431,7 @@
         <v>0.022831050228310501</v>
       </c>
       <c r="N5" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15">
@@ -13442,31 +13442,31 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G6" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L6">
         <v>0.022831050228310501</v>
@@ -13475,7 +13475,7 @@
         <v>0.022831050228310501</v>
       </c>
       <c r="N6" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15">
@@ -13486,31 +13486,31 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G7" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L7">
         <v>0.0232876712328767</v>
@@ -13519,7 +13519,7 @@
         <v>0.0232876712328767</v>
       </c>
       <c r="N7" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15">
@@ -13530,31 +13530,31 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G8" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L8">
         <v>0.022831050228310501</v>
@@ -13563,7 +13563,7 @@
         <v>0.022831050228310501</v>
       </c>
       <c r="N8" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15">
@@ -13574,31 +13574,31 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G9" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L9">
         <v>0.022831050228310501</v>
@@ -13607,7 +13607,7 @@
         <v>0.022831050228310501</v>
       </c>
       <c r="N9" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15">
@@ -13618,31 +13618,31 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G10" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H10" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I10" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J10" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K10" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L10">
         <v>0.022831050228310501</v>
@@ -13651,7 +13651,7 @@
         <v>0.022831050228310501</v>
       </c>
       <c r="N10" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15">
@@ -13662,31 +13662,31 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G11" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I11" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J11" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K11" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L11">
         <v>0.022831050228310501</v>
@@ -13695,7 +13695,7 @@
         <v>0.022831050228310501</v>
       </c>
       <c r="N11" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15">
@@ -13706,31 +13706,31 @@
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G12" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L12">
         <v>0.022831050228310501</v>
@@ -13739,7 +13739,7 @@
         <v>0.022831050228310501</v>
       </c>
       <c r="N12" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15">
@@ -13750,31 +13750,31 @@
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G13" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L13">
         <v>0.022831050228310501</v>
@@ -13783,7 +13783,7 @@
         <v>0.022831050228310501</v>
       </c>
       <c r="N13" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15">
@@ -13794,31 +13794,31 @@
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G14" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L14">
         <v>0.022831050228310501</v>
@@ -13827,7 +13827,7 @@
         <v>0.022831050228310501</v>
       </c>
       <c r="N14" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15">
@@ -13838,31 +13838,31 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="G15" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L15">
         <v>0.022831050228310501</v>
@@ -13871,7 +13871,7 @@
         <v>0.022831050228310501</v>
       </c>
       <c r="N15" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15">
@@ -13879,34 +13879,34 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C16" t="s">
+        <v>259</v>
+      </c>
+      <c r="D16" t="s">
+        <v>227</v>
+      </c>
+      <c r="E16" t="s">
+        <v>227</v>
+      </c>
+      <c r="F16" t="s">
+        <v>245</v>
+      </c>
+      <c r="G16" t="s">
         <v>229</v>
       </c>
-      <c r="D16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" t="s">
-        <v>215</v>
-      </c>
-      <c r="G16" t="s">
-        <v>213</v>
-      </c>
       <c r="H16" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I16" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J16" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K16" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L16">
         <v>0.33000000000000002</v>
@@ -13915,7 +13915,7 @@
         <v>0.33000000000000002</v>
       </c>
       <c r="N16" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15">
@@ -13923,34 +13923,34 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C17" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F17" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G17" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H17" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I17" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J17" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K17" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L17">
         <v>0.33000000000000002</v>
@@ -13959,7 +13959,7 @@
         <v>0.33000000000000002</v>
       </c>
       <c r="N17" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15">
@@ -13967,34 +13967,34 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C18" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F18" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G18" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H18" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I18" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J18" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K18" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L18">
         <v>0.77915338816094504</v>
@@ -14003,7 +14003,7 @@
         <v>0.77915338816094504</v>
       </c>
       <c r="N18" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15">
@@ -14011,34 +14011,34 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C19" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F19" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G19" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H19" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I19" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J19" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K19" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L19">
         <v>0.63024757853709501</v>
@@ -14047,7 +14047,7 @@
         <v>0.63024757853709501</v>
       </c>
       <c r="N19" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15">
@@ -14055,34 +14055,34 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C20" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="D20" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F20" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G20" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H20" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I20" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J20" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K20" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L20">
         <v>0.33000000000000002</v>
@@ -14091,7 +14091,7 @@
         <v>0.33000000000000002</v>
       </c>
       <c r="N20" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="15">
@@ -14099,34 +14099,34 @@
         <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C21" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F21" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G21" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H21" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I21" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J21" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K21" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L21">
         <v>0.59834963673469899</v>
@@ -14135,7 +14135,7 @@
         <v>0.59834963673469899</v>
       </c>
       <c r="N21" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15">
@@ -14143,34 +14143,34 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C22" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F22" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G22" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H22" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I22" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J22" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K22" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L22">
         <v>1</v>
@@ -14179,7 +14179,7 @@
         <v>1</v>
       </c>
       <c r="N22" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="15">
@@ -14187,34 +14187,34 @@
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C23" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F23" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G23" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H23" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I23" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J23" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K23" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L23">
         <v>0.33000000000000002</v>
@@ -14223,7 +14223,7 @@
         <v>0.33000000000000002</v>
       </c>
       <c r="N23" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="15">
@@ -14231,34 +14231,34 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C24" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F24" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G24" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H24" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I24" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J24" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K24" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L24">
         <v>0.33000000000000002</v>
@@ -14267,7 +14267,7 @@
         <v>0.33000000000000002</v>
       </c>
       <c r="N24" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="15">
@@ -14275,34 +14275,34 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C25" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="D25" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F25" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G25" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H25" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I25" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J25" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K25" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L25">
         <v>0.77915338816094504</v>
@@ -14311,7 +14311,7 @@
         <v>0.77915338816094504</v>
       </c>
       <c r="N25" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15">
@@ -14319,34 +14319,34 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C26" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="D26" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F26" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G26" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H26" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I26" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J26" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K26" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L26">
         <v>0.63024757853709501</v>
@@ -14355,7 +14355,7 @@
         <v>0.63024757853709501</v>
       </c>
       <c r="N26" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="15">
@@ -14363,34 +14363,34 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C27" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="D27" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E27" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F27" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G27" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H27" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I27" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J27" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K27" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L27">
         <v>0.33000000000000002</v>
@@ -14399,7 +14399,7 @@
         <v>0.33000000000000002</v>
       </c>
       <c r="N27" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="15">
@@ -14407,34 +14407,34 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="D28" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F28" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G28" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H28" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I28" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J28" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K28" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L28">
         <v>0.59834963673469899</v>
@@ -14443,7 +14443,7 @@
         <v>0.59834963673469899</v>
       </c>
       <c r="N28" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="15">
@@ -14451,34 +14451,34 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C29" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="F29" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="G29" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H29" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="I29" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="J29" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="K29" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
       <c r="L29">
         <v>1</v>
@@ -14487,7 +14487,7 @@
         <v>1</v>
       </c>
       <c r="N29" t="s">
-        <v>17</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
